--- a/Filtered/HCA_Florida_University_Hospital.xlsx
+++ b/Filtered/HCA_Florida_University_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1326,6 +1381,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1862,6 +1957,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1919,6 +2019,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2708,6 +2868,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2842,6 +3012,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2976,6 +3156,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3038,6 +3223,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3095,6 +3285,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3172,6 +3367,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3229,6 +3429,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3363,6 +3573,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3497,6 +3717,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3631,6 +3861,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3765,6 +4005,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3976,6 +4231,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4110,6 +4375,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4244,6 +4519,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4378,6 +4663,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4512,6 +4807,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4589,6 +4889,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4646,6 +4951,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4723,6 +5033,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4780,6 +5095,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4857,6 +5177,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4914,6 +5239,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4991,6 +5321,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5048,6 +5383,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5125,6 +5465,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5182,6 +5527,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5259,6 +5609,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5316,6 +5671,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5393,6 +5753,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5450,6 +5815,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5527,6 +5897,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5584,6 +5959,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5661,6 +6041,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5718,6 +6103,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5795,6 +6185,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5852,6 +6247,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5914,6 +6314,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5971,6 +6376,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6048,6 +6458,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6105,6 +6520,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6182,6 +6602,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6239,6 +6664,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6316,6 +6746,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6373,6 +6808,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6450,6 +6890,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6507,6 +6952,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6584,6 +7034,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6641,6 +7096,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6718,6 +7178,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6775,6 +7240,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6852,6 +7322,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6909,6 +7384,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6986,6 +7466,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7043,6 +7528,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7120,6 +7610,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7177,6 +7672,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7254,6 +7754,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7311,6 +7816,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7388,6 +7898,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7445,6 +7960,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7522,6 +8042,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7579,6 +8104,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7656,6 +8186,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7713,6 +8248,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7790,6 +8330,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7847,6 +8392,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7924,6 +8474,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7981,6 +8536,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8058,6 +8618,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8115,6 +8680,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8192,6 +8762,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8249,6 +8824,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8326,6 +8906,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8383,6 +8968,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8460,6 +9050,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8517,6 +9112,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8594,6 +9194,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8671,6 +9276,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8728,6 +9338,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8805,6 +9420,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8882,6 +9502,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8939,6 +9564,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9016,6 +9646,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9073,6 +9708,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9150,6 +9790,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9227,6 +9872,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9284,6 +9934,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9361,6 +10016,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9418,6 +10078,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9495,6 +10160,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9572,6 +10242,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9629,6 +10304,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9706,6 +10386,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9763,6 +10448,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9840,6 +10530,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9897,6 +10592,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9974,6 +10674,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10031,6 +10736,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10093,6 +10803,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10150,6 +10865,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10212,6 +10932,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10274,6 +10999,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10331,6 +11061,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10408,6 +11143,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10465,6 +11205,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10542,6 +11287,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10599,6 +11349,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10676,6 +11431,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10733,6 +11493,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10810,6 +11575,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10867,6 +11637,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10944,6 +11719,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11001,6 +11781,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11078,6 +11863,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11135,6 +11925,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11212,6 +12007,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11269,6 +12069,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11346,6 +12151,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11403,6 +12213,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11480,6 +12295,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11537,6 +12357,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11614,6 +12439,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11671,6 +12501,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11748,6 +12583,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11805,6 +12645,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11882,6 +12727,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11939,6 +12789,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12016,6 +12871,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12073,6 +12933,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12150,6 +13015,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12207,6 +13077,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12284,6 +13159,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12361,6 +13241,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12418,6 +13303,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12480,6 +13370,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12537,6 +13432,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12599,6 +13499,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12656,6 +13561,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12733,6 +13643,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12790,6 +13705,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12867,6 +13787,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12924,6 +13849,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13001,6 +13931,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13058,6 +13993,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13135,6 +14075,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13192,6 +14137,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13269,6 +14219,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13326,6 +14281,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13403,6 +14363,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13460,6 +14425,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13537,6 +14507,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13594,6 +14569,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13671,6 +14651,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13728,6 +14713,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13805,6 +14795,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13862,6 +14857,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13939,6 +14939,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13996,6 +15001,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14073,6 +15083,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14130,6 +15145,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14207,6 +15227,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14264,6 +15289,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14341,6 +15371,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14398,6 +15433,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14475,6 +15515,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14532,6 +15577,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14609,6 +15659,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14666,6 +15721,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14743,6 +15803,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14800,6 +15865,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14877,6 +15947,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14934,6 +16009,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15011,6 +16091,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15068,6 +16153,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15145,6 +16235,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15202,6 +16297,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15279,6 +16379,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15336,6 +16441,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15413,6 +16523,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15470,6 +16585,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15547,6 +16667,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15604,6 +16729,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15681,6 +16811,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15738,6 +16873,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15815,6 +16955,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15872,6 +17017,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15949,6 +17099,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16006,6 +17161,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16083,6 +17243,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16140,6 +17305,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16217,6 +17387,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16274,6 +17449,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16351,6 +17531,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16408,6 +17593,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16470,6 +17660,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16527,6 +17722,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16604,6 +17804,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16661,6 +17866,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16738,6 +17948,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16795,6 +18010,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16872,6 +18092,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16929,6 +18154,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17006,6 +18236,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17063,6 +18298,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17140,6 +18380,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17217,6 +18462,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17274,6 +18524,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17351,6 +18606,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17408,6 +18668,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17485,6 +18750,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17542,6 +18812,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17619,6 +18894,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17676,6 +18956,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17753,6 +19038,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17810,6 +19100,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17887,6 +19182,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17944,6 +19244,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18021,6 +19326,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18078,6 +19388,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18155,6 +19470,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18212,6 +19532,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18289,6 +19614,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18346,6 +19676,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18423,6 +19758,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18480,6 +19820,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18557,6 +19902,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18614,6 +19964,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18691,6 +20046,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18748,6 +20108,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18825,6 +20190,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18882,6 +20252,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18959,6 +20334,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19016,6 +20396,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19093,6 +20478,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19150,6 +20540,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19227,6 +20622,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19284,6 +20684,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19361,6 +20766,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19438,6 +20848,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19495,6 +20910,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19572,6 +20992,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19629,6 +21054,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19706,6 +21136,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19763,6 +21198,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19840,6 +21280,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19897,6 +21342,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19974,6 +21424,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20031,6 +21486,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20108,6 +21568,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20185,6 +21650,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20242,6 +21712,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20319,6 +21794,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20376,6 +21856,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20453,6 +21938,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20530,6 +22020,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20587,6 +22082,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20664,6 +22164,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20721,6 +22226,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20798,6 +22308,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20855,6 +22370,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20932,6 +22452,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20989,6 +22514,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21066,6 +22596,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21123,6 +22658,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21200,6 +22740,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21257,6 +22802,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21334,6 +22884,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21391,6 +22946,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21453,6 +23013,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21510,6 +23075,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21587,6 +23157,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21644,6 +23219,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21721,6 +23301,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21778,6 +23363,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21855,6 +23445,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21912,6 +23507,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21974,6 +23574,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22031,6 +23636,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22108,6 +23718,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22165,6 +23780,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22227,6 +23847,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22284,6 +23909,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22361,6 +23991,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22418,6 +24053,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22495,6 +24135,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22552,6 +24197,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22629,6 +24279,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22686,6 +24341,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22763,6 +24423,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22820,6 +24485,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22882,6 +24552,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22939,6 +24614,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23016,6 +24696,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23073,6 +24758,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23150,6 +24840,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23207,6 +24902,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23284,6 +24984,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23341,6 +25046,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23418,6 +25128,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23475,6 +25190,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23552,6 +25272,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23609,6 +25334,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23686,6 +25416,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23743,6 +25478,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23820,6 +25560,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23877,6 +25622,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23954,6 +25704,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24011,6 +25766,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24073,6 +25833,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24130,6 +25895,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24207,6 +25977,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24264,6 +26039,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24341,6 +26121,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24398,6 +26183,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24475,6 +26265,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24532,6 +26327,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24609,6 +26409,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24666,6 +26471,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24743,6 +26553,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24800,6 +26615,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24877,6 +26697,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24934,6 +26759,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25011,6 +26841,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25068,6 +26903,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25145,6 +26985,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25202,6 +27047,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25279,6 +27129,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25336,6 +27191,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25413,6 +27273,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25470,6 +27335,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25547,6 +27417,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25604,6 +27479,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25681,6 +27561,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25738,6 +27623,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25815,6 +27705,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25872,6 +27767,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25949,6 +27849,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26006,6 +27911,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26068,6 +27978,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26130,6 +28045,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26187,6 +28107,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26264,6 +28189,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26321,6 +28251,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26383,6 +28318,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26445,6 +28385,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26507,6 +28452,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26569,6 +28519,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26631,6 +28586,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26688,6 +28648,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26765,6 +28730,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26822,6 +28792,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26899,6 +28874,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26956,6 +28936,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27018,6 +29003,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27080,6 +29070,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27137,6 +29132,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27214,6 +29214,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27271,6 +29276,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27348,6 +29358,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27405,6 +29420,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27467,6 +29487,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27524,6 +29549,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27586,6 +29616,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27648,6 +29683,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27710,6 +29750,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27767,6 +29812,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27844,6 +29894,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27901,6 +29956,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27963,6 +30023,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28025,6 +30090,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28087,6 +30157,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28144,6 +30219,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28206,6 +30286,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28268,6 +30353,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28330,6 +30420,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28387,6 +30482,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28464,6 +30564,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28521,6 +30626,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28583,6 +30693,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28640,6 +30755,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28717,6 +30837,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28774,6 +30899,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28836,6 +30966,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28898,6 +31033,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28960,6 +31100,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29017,6 +31162,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29094,6 +31244,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29151,6 +31306,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29228,6 +31388,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29285,6 +31450,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29347,6 +31517,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29409,6 +31584,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29466,6 +31646,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29528,6 +31713,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29590,6 +31780,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29652,6 +31847,11 @@
           <t>COCUHA</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29707,6 +31907,11 @@
       <c r="K442" t="inlineStr">
         <is>
           <t>COCUHA</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
